--- a/summary/no/exposures_meta_analysis_clear_cell_renal_cell_carcinoma_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_clear_cell_renal_cell_carcinoma_dietary.xlsx
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,13 +60,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -452,57 +464,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -514,28 +526,28 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="4" t="n">
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
         <v>549</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -545,28 +557,28 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="4" t="n">
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
         <v>549</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>250</v>
       </c>
     </row>
@@ -576,28 +588,28 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>1.24</v>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="4" t="n">
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="3" t="n">
         <v>120852</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>297</v>
       </c>
     </row>

--- a/summary/no/exposures_meta_analysis_clear_cell_renal_cell_carcinoma_dietary.xlsx
+++ b/summary/no/exposures_meta_analysis_clear_cell_renal_cell_carcinoma_dietary.xlsx
@@ -23,16 +23,13 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,22 +57,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,57 +452,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number estimates</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -526,28 +514,28 @@
           <t>green_tea</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="5" t="n">
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="6" t="inlineStr"/>
-      <c r="J2" s="3" t="n">
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
         <v>549</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -557,28 +545,28 @@
           <t>tea</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="5" t="n">
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="3" t="n">
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
         <v>549</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>250</v>
       </c>
     </row>
@@ -588,28 +576,28 @@
           <t>alcohol</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.48</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="5" t="n">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="3" t="n">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
         <v>120852</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="2" t="n">
         <v>297</v>
       </c>
     </row>
